--- a/examples/segment/Thornhill_Segment_Config_Explore.xlsx
+++ b/examples/segment/Thornhill_Segment_Config_Explore.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t xml:space="preserve">Setting</t>
   </si>
@@ -246,7 +246,7 @@
     <t xml:space="preserve">analyst_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Turas worked example</t>
+    <t xml:space="preserve">Example analyst</t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t xml:space="preserve">The Research LampPost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thornhill Grocers</t>
   </si>
   <si>
     <t xml:space="preserve">Variable</t>
@@ -1040,6 +1046,14 @@
         <v>81</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1057,58 +1071,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/examples/segment/Thornhill_Segment_Config_Explore.xlsx
+++ b/examples/segment/Thornhill_Segment_Config_Explore.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t xml:space="preserve">Setting</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tabs_export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
   </si>
   <si>
     <t xml:space="preserve">segment_names</t>
@@ -843,23 +849,23 @@
         <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -883,12 +889,12 @@
         <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -896,7 +902,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -904,7 +910,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
@@ -912,7 +918,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
@@ -920,7 +926,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
@@ -928,7 +934,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
@@ -936,7 +942,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
         <v>31</v>
@@ -944,7 +950,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
         <v>31</v>
@@ -952,7 +958,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
         <v>31</v>
@@ -960,7 +966,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
         <v>31</v>
@@ -968,7 +974,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
         <v>31</v>
@@ -976,10 +982,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
@@ -987,12 +993,12 @@
         <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
         <v>31</v>
@@ -1000,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
@@ -1011,15 +1017,15 @@
         <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
@@ -1052,6 +1058,14 @@
       </c>
       <c r="B51" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1071,58 +1085,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/examples/segment/Thornhill_Segment_Config_Explore.xlsx
+++ b/examples/segment/Thornhill_Segment_Config_Explore.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">k_selection_metrics</t>
   </si>
   <si>
-    <t xml:space="preserve">silhouette,elbow</t>
+    <t xml:space="preserve">silhouette,elbow,calinski_harabasz,davies_bouldin</t>
   </si>
   <si>
     <t xml:space="preserve">nstart</t>
